--- a/artfynd/A 31667-2021 artfynd.xlsx
+++ b/artfynd/A 31667-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31667-2021 artfynd.xlsx
+++ b/artfynd/A 31667-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105536573</v>
+        <v>105536591</v>
       </c>
       <c r="B2" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>900222.8819079072</v>
+        <v>900312</v>
       </c>
       <c r="R2" t="n">
-        <v>7317712.065647352</v>
+        <v>7317435</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +743,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105536589</v>
+        <v>105536586</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>900283.6238535884</v>
+        <v>900108</v>
       </c>
       <c r="R3" t="n">
-        <v>7317436.58721067</v>
+        <v>7317399</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +840,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105536574</v>
+        <v>105536587</v>
       </c>
       <c r="B4" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>900210.968553161</v>
+        <v>900073</v>
       </c>
       <c r="R4" t="n">
-        <v>7317710.810797466</v>
+        <v>7317402</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -972,19 +937,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105536593</v>
+        <v>105536588</v>
       </c>
       <c r="B5" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,45 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Seskarö, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>900276.7975427527</v>
+        <v>900335</v>
       </c>
       <c r="R5" t="n">
-        <v>7317547.650450195</v>
+        <v>7317474</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,40 +1034,19 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Hed med tall</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tallhed med äldre tallskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105536576</v>
+        <v>105536567</v>
       </c>
       <c r="B6" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>900104.008284909</v>
+        <v>900291</v>
       </c>
       <c r="R6" t="n">
-        <v>7317388.490361447</v>
+        <v>7317520</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1218,19 +1131,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105536571</v>
+        <v>105536589</v>
       </c>
       <c r="B7" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>900332.2616458671</v>
+        <v>900283</v>
       </c>
       <c r="R7" t="n">
-        <v>7317767.386770424</v>
+        <v>7317437</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1330,19 +1228,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105536572</v>
+        <v>105536590</v>
       </c>
       <c r="B8" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>900241.6463738785</v>
+        <v>900314</v>
       </c>
       <c r="R8" t="n">
-        <v>7317720.944125236</v>
+        <v>7317418</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1442,19 +1325,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105536585</v>
+        <v>105536568</v>
       </c>
       <c r="B9" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>900291.274391741</v>
+        <v>900141</v>
       </c>
       <c r="R9" t="n">
-        <v>7317524.695786059</v>
+        <v>7317474</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1554,19 +1422,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105536575</v>
+        <v>105536569</v>
       </c>
       <c r="B10" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>900100.8012023324</v>
+        <v>900333</v>
       </c>
       <c r="R10" t="n">
-        <v>7317411.361266868</v>
+        <v>7317424</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1666,19 +1519,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105536581</v>
+        <v>105536570</v>
       </c>
       <c r="B11" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>900069.760073651</v>
+        <v>900293</v>
       </c>
       <c r="R11" t="n">
-        <v>7317397.847047225</v>
+        <v>7317776</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1778,19 +1616,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105536582</v>
+        <v>105536571</v>
       </c>
       <c r="B12" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>900111.1505963115</v>
+        <v>900332</v>
       </c>
       <c r="R12" t="n">
-        <v>7317459.45325462</v>
+        <v>7317767</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1890,19 +1713,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105536578</v>
+        <v>105536572</v>
       </c>
       <c r="B13" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>900052.8324725801</v>
+        <v>900242</v>
       </c>
       <c r="R13" t="n">
-        <v>7317399.63799144</v>
+        <v>7317721</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2002,19 +1810,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105536591</v>
+        <v>105536573</v>
       </c>
       <c r="B14" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1593</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>900312.5807363826</v>
+        <v>900222</v>
       </c>
       <c r="R14" t="n">
-        <v>7317435.235982021</v>
+        <v>7317712</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2114,19 +1907,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105536567</v>
+        <v>105536574</v>
       </c>
       <c r="B15" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>900291.5530973456</v>
+        <v>900211</v>
       </c>
       <c r="R15" t="n">
-        <v>7317519.737716482</v>
+        <v>7317711</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2226,19 +2004,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105536587</v>
+        <v>105536575</v>
       </c>
       <c r="B16" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2305,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>900072.9245560546</v>
+        <v>900100</v>
       </c>
       <c r="R16" t="n">
-        <v>7317402.038698217</v>
+        <v>7317411</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2338,19 +2101,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105536584</v>
+        <v>105536576</v>
       </c>
       <c r="B17" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>900109.8572755002</v>
+        <v>900104</v>
       </c>
       <c r="R17" t="n">
-        <v>7317477.594829485</v>
+        <v>7317388</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2450,19 +2198,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105536586</v>
+        <v>105536578</v>
       </c>
       <c r="B18" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>900107.8919149269</v>
+        <v>900053</v>
       </c>
       <c r="R18" t="n">
-        <v>7317399.445964258</v>
+        <v>7317400</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2562,19 +2295,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105536590</v>
+        <v>105536579</v>
       </c>
       <c r="B19" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2641,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>900313.7607079718</v>
+        <v>900075</v>
       </c>
       <c r="R19" t="n">
-        <v>7317417.910833304</v>
+        <v>7317402</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2674,19 +2392,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105536579</v>
+        <v>105536580</v>
       </c>
       <c r="B20" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>900075.843937614</v>
+        <v>900049</v>
       </c>
       <c r="R20" t="n">
-        <v>7317402.031603411</v>
+        <v>7317408</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2786,19 +2489,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105536588</v>
+        <v>105536581</v>
       </c>
       <c r="B21" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>900335.0469273475</v>
+        <v>900070</v>
       </c>
       <c r="R21" t="n">
-        <v>7317474.202118104</v>
+        <v>7317398</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2898,19 +2586,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,61 +2615,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105536592</v>
+        <v>105536582</v>
       </c>
       <c r="B22" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Seskarö, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>900119.719300601</v>
+        <v>900111</v>
       </c>
       <c r="R22" t="n">
-        <v>7317475.646387346</v>
+        <v>7317459</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3021,40 +2683,19 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Lavhed</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Lavhed med äldre tallskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3071,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105536568</v>
+        <v>105536584</v>
       </c>
       <c r="B23" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>900140.7924867717</v>
+        <v>900110</v>
       </c>
       <c r="R23" t="n">
-        <v>7317474.020947293</v>
+        <v>7317477</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3144,19 +2780,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105536569</v>
+        <v>105536585</v>
       </c>
       <c r="B24" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>900332.4619829177</v>
+        <v>900291</v>
       </c>
       <c r="R24" t="n">
-        <v>7317424.282711679</v>
+        <v>7317525</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3256,19 +2877,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,6 +2903,244 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>105536592</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Seskarö, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>900120</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7317475</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nedertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Lavhed</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Lavhed med äldre tallskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>105536593</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Seskarö, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>900277</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7317548</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nedertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Hed med tall</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Tallhed med äldre tallskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
